--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.68033897317891</v>
+        <v>7.910555083141573</v>
       </c>
       <c r="D2" t="n">
-        <v>41.1992986990601</v>
+        <v>6.694886038597267</v>
       </c>
       <c r="E2" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F2" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.57556234372061</v>
+        <v>5.618528880854599</v>
       </c>
       <c r="D3" t="n">
-        <v>25.79537151989264</v>
+        <v>4.191747871982555</v>
       </c>
       <c r="E3" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F3" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69847233931271</v>
+        <v>6.938501755138315</v>
       </c>
       <c r="D4" t="n">
-        <v>43.04148839966737</v>
+        <v>6.994241864945948</v>
       </c>
       <c r="E4" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F4" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.16934211537941</v>
+        <v>5.715018093749155</v>
       </c>
       <c r="D5" t="n">
-        <v>35.56769834765199</v>
+        <v>5.779750981493449</v>
       </c>
       <c r="E5" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F5" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.32158660219745</v>
+        <v>3.952257822857085</v>
       </c>
       <c r="D6" t="n">
-        <v>23.74183135760629</v>
+        <v>3.858047595611023</v>
       </c>
       <c r="E6" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F6" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.16758105220504</v>
+        <v>6.85223192098332</v>
       </c>
       <c r="D7" t="n">
-        <v>42.64061692518518</v>
+        <v>6.929100250342593</v>
       </c>
       <c r="E7" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F7" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>29.96442596755083</v>
+        <v>4.869219219727011</v>
       </c>
       <c r="D8" t="n">
-        <v>29.99554106507718</v>
+        <v>4.874275423075042</v>
       </c>
       <c r="E8" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F8" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.27903169845808</v>
+        <v>3.620342650999438</v>
       </c>
       <c r="D9" t="n">
-        <v>22.65209055482562</v>
+        <v>3.680964715159164</v>
       </c>
       <c r="E9" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F9" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>44.9676452962398</v>
+        <v>7.307242360638968</v>
       </c>
       <c r="D10" t="n">
-        <v>29.4346300048025</v>
+        <v>4.783127375780406</v>
       </c>
       <c r="E10" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F10" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.97409795417541</v>
+        <v>7.145790917553505</v>
       </c>
       <c r="D11" t="n">
-        <v>43.47809508703484</v>
+        <v>7.065190451643161</v>
       </c>
       <c r="E11" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F11" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.55671641276068</v>
+        <v>4.802966417073611</v>
       </c>
       <c r="D12" t="n">
-        <v>30.11861177089932</v>
+        <v>4.89427441277114</v>
       </c>
       <c r="E12" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F12" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.309419739974658</v>
+        <v>1.350280707745882</v>
       </c>
       <c r="D13" t="n">
-        <v>8.846074714346528</v>
+        <v>1.437487141081311</v>
       </c>
       <c r="E13" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F13" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.31589695724701</v>
+        <v>6.551333255552638</v>
       </c>
       <c r="D14" t="n">
-        <v>34.92009045502646</v>
+        <v>5.6745146989418</v>
       </c>
       <c r="E14" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F14" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>36.4489372433574</v>
+        <v>5.922952302045577</v>
       </c>
       <c r="D15" t="n">
-        <v>19.27418455837331</v>
+        <v>3.132054990735663</v>
       </c>
       <c r="E15" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F15" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>33.76975186874083</v>
+        <v>5.487584678670385</v>
       </c>
       <c r="D16" t="n">
-        <v>34.20682147493348</v>
+        <v>5.55860848967669</v>
       </c>
       <c r="E16" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F16" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>17.42175781579535</v>
+        <v>2.831035645066745</v>
       </c>
       <c r="D17" t="n">
-        <v>17.69080841114836</v>
+        <v>2.874756366811608</v>
       </c>
       <c r="E17" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F17" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>15.65786304284418</v>
+        <v>2.54440274446218</v>
       </c>
       <c r="D18" t="n">
-        <v>15.45047093009306</v>
+        <v>2.510701526140123</v>
       </c>
       <c r="E18" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F18" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>25.98007319108439</v>
+        <v>4.221761893551213</v>
       </c>
       <c r="D19" t="n">
-        <v>26.29190191848297</v>
+        <v>4.272434061753482</v>
       </c>
       <c r="E19" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F19" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>25.2222996261765</v>
+        <v>4.098623689253681</v>
       </c>
       <c r="D20" t="n">
-        <v>25.31014842604732</v>
+        <v>4.11289911923269</v>
       </c>
       <c r="E20" t="n">
-        <v>10.76228688164381</v>
+        <v>1.748871618267119</v>
       </c>
       <c r="F20" t="n">
-        <v>9.626497829196255</v>
+        <v>1.564305897244392</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
